--- a/inst/extdata/Common_Safety_Displays_cards.xlsx
+++ b/inst/extdata/Common_Safety_Displays_cards.xlsx
@@ -1,42 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clymb-my.sharepoint.com/personal/mbosman_clymb_onmicrosoft_com/Documents/Documents/siera/inst/extdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="13_ncr:1_{65D881D3-B504-42B3-944D-AEE34ED84ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D962C3D-8258-4EBA-9A80-70440A8B8665}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" firstSheet="10" activeTab="13" xr2:uid="{0614A9B4-62F8-4E97-B269-DF8F18CCF706}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
-    <sheet name="ReportingEvent" sheetId="19" r:id="rId1"/>
-    <sheet name="ReferenceDocuments" sheetId="20" r:id="rId2"/>
-    <sheet name="Categorizations" sheetId="22" r:id="rId3"/>
-    <sheet name="MainListOfContents" sheetId="10" r:id="rId4"/>
-    <sheet name="OtherListsOfContents" sheetId="25" r:id="rId5"/>
-    <sheet name="GlobalDisplaySections" sheetId="35" r:id="rId6"/>
-    <sheet name="Outputs" sheetId="11" r:id="rId7"/>
-    <sheet name="OutputFiles" sheetId="36" r:id="rId8"/>
-    <sheet name="Displays" sheetId="13" r:id="rId9"/>
-    <sheet name="OutputProgrammingCode" sheetId="30" r:id="rId10"/>
-    <sheet name="OutputCodeParameters" sheetId="34" r:id="rId11"/>
-    <sheet name="OutputDocumentRefs" sheetId="31" r:id="rId12"/>
-    <sheet name="DataSubsets" sheetId="6" r:id="rId13"/>
-    <sheet name="AnalysisSets" sheetId="1" r:id="rId14"/>
-    <sheet name="AnalysisGroupings" sheetId="2" r:id="rId15"/>
-    <sheet name="Analyses" sheetId="3" r:id="rId16"/>
-    <sheet name="AnalysisProgrammingCode" sheetId="27" r:id="rId17"/>
-    <sheet name="AnalysisCodeParameters" sheetId="32" r:id="rId18"/>
-    <sheet name="AnalysisDocumentRefs" sheetId="24" r:id="rId19"/>
-    <sheet name="AnalysisMethods" sheetId="4" r:id="rId20"/>
-    <sheet name="AnalysisMethodCodeTemplate" sheetId="23" r:id="rId21"/>
-    <sheet name="AnalysisMethodCodeParameters" sheetId="33" r:id="rId22"/>
-    <sheet name="AnalysisMethodDocumentRefs" sheetId="26" r:id="rId23"/>
-    <sheet name="TerminologyExtensions" sheetId="21" r:id="rId24"/>
+    <sheet name="ReportingEvent" sheetId="19" state="visible" r:id="rId1"/>
+    <sheet name="ReferenceDocuments" sheetId="20" state="visible" r:id="rId2"/>
+    <sheet name="Categorizations" sheetId="22" state="visible" r:id="rId3"/>
+    <sheet name="MainListOfContents" sheetId="10" state="visible" r:id="rId4"/>
+    <sheet name="OtherListsOfContents" sheetId="25" state="visible" r:id="rId5"/>
+    <sheet name="GlobalDisplaySections" sheetId="35" state="visible" r:id="rId6"/>
+    <sheet name="Outputs" sheetId="11" state="visible" r:id="rId7"/>
+    <sheet name="OutputFiles" sheetId="36" state="visible" r:id="rId8"/>
+    <sheet name="Displays" sheetId="13" state="visible" r:id="rId9"/>
+    <sheet name="OutputProgrammingCode" sheetId="30" state="visible" r:id="rId10"/>
+    <sheet name="OutputCodeParameters" sheetId="34" state="visible" r:id="rId11"/>
+    <sheet name="OutputDocumentRefs" sheetId="31" state="visible" r:id="rId12"/>
+    <sheet name="DataSubsets" sheetId="6" state="visible" r:id="rId13"/>
+    <sheet name="AnalysisSets" sheetId="1" state="visible" r:id="rId14"/>
+    <sheet name="AnalysisGroupings" sheetId="2" state="visible" r:id="rId15"/>
+    <sheet name="Analyses" sheetId="3" state="visible" r:id="rId16"/>
+    <sheet name="AnalysisProgrammingCode" sheetId="27" state="visible" r:id="rId17"/>
+    <sheet name="AnalysisCodeParameters" sheetId="32" state="visible" r:id="rId18"/>
+    <sheet name="AnalysisDocumentRefs" sheetId="24" state="visible" r:id="rId19"/>
+    <sheet name="AnalysisMethods" sheetId="4" state="visible" r:id="rId20"/>
+    <sheet name="AnalysisMethodCodeTemplate" sheetId="23" state="visible" r:id="rId21"/>
+    <sheet name="AnalysisMethodCodeParameters" sheetId="33" state="visible" r:id="rId22"/>
+    <sheet name="AnalysisMethodDocumentRefs" sheetId="26" state="visible" r:id="rId23"/>
+    <sheet name="TerminologyExtensions" sheetId="21" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Analyses!$A$1:$W$24</definedName>
@@ -48,32 +41,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">OutputDocumentRefs!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Richard</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{44ED35CB-7EEE-4AA9-9B4E-6D9C40C1D98F}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -82,7 +59,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
+          <t xml:space="preserve">Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
         </r>
       </text>
     </comment>
@@ -90,13 +67,13 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments19.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Richard</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{74B1AA6A-6FD2-4F74-AD45-9C05B7586857}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
+          <t xml:space="preserve">Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
         </r>
       </text>
     </comment>
@@ -113,13 +90,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments23.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Richard</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{BA7913E3-38B4-45EB-9040-CFA873D860CF}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -128,7 +105,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
+          <t xml:space="preserve">Page range n-n (e.g., 6-12), pipe-delmited list of page numbers (e.g., 2|8|12), or pipe-delimited list of named destinations (e.g., Section 2|Section 5).</t>
         </r>
       </text>
     </comment>
@@ -137,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
   <si>
     <t>id</t>
   </si>
@@ -2050,12 +2027,80 @@
 dplyr::mutate(operationid = dplyr::case_when(stat_name == 'n' ~ 'Mth01_CatVar_Summ_ByGrp_1_n',
                                                               stat_name == 'p' ~ 'Mth01_CatVar_Summ_ByGrp_2_pct'))</t>
   </si>
+  <si>
+    <t xml:space="preserve">in_data = df2_analysisidhere |&gt;
+    dplyr::select(anavarhere, groupvar1here) |&gt;
+    unique()
+df3_analysisidhere &lt;-
+  cards::ard_tabulate(
+    data = in_data
+    bystmthere
+  ) |&gt;
+dplyr::filter(stat_name == 'n') |&gt;
+ dplyr::mutate(operationid = 'Mth01_CatVar_Count_ByGrp_1_n')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">denom_dataset = df2_denomanaidhere |&gt;
+  dplyr::select(denom_anagroupvarshere)
+in_data = df2_analysisidhere |&gt;
+    dplyr::distinct(distinctlisthere) |&gt;
+    dplyr::mutate(dummy = 'dummyvar')
+dataDriven = isdatadrivenhere
+if(dataDriven == TRUE){
+df3_analysisidhere &lt;-
+  cards::ard_tabulate(
+    data = in_data,
+    strata = c(byvarshere),
+    variables = 'dummy',
+    denominator = denom_dataset
+  ) } else {
+df3_analysisidhere &lt;-
+ cards::ard_tabulate(
+    data = in_data,
+    by = c(byvarshere),
+    variables = 'dummy',
+    denominator = denom_dataset
+  ) }
+df3_analysisidhere &lt;- df3_analysisidhere|&gt;
+dplyr::filter(stat_name %in% c('n', 'p')) |&gt;
+dplyr::mutate(operationid = dplyr::case_when(stat_name == 'n' ~ 'Mth01_CatVar_Summ_ByGrp_1_n',
+                                                              stat_name == 'p' ~ 'Mth01_CatVar_Summ_ByGrp_2_pct'))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df3_analysisidhere &lt;-
+  cards::ard_summary(
+    data = df2_analysisidhere,
+    by = c(byvarshere),
+    variables = anavarhere
+  ) |&gt;
+dplyr::mutate(operationid = dplyr::case_when(stat_name == 'N' ~ 'Mth02_ContVar_Summ_ByGrp_1_n',
+                                                                     stat_name == 'mean' ~ 'Mth02_ContVar_Summ_ByGrp_2_Mean',
+                                                                     stat_name == 'sd' ~ 'Mth02_ContVar_Summ_ByGrp_3_SD',
+                                                                     stat_name == 'median' ~ 'Mth02_ContVar_Summ_ByGrp_4_Median',
+                                                                     stat_name == 'p25' ~ 'Mth02_ContVar_Summ_ByGrp_5_Q1',
+                                                                     stat_name == 'p75' ~ 'Mth02_ContVar_Summ_ByGrp_6_Q3',
+                                                                     stat_name == 'min' ~ 'Mth02_ContVar_Summ_ByGrp_7_Min',
+                                                                     stat_name == 'max' ~ 'Mth02_ContVar_Summ_ByGrp_8_Max'))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df3_analysisidhere &lt;- 
+    cardx::ard_stats_chisq_test(by = groupvar1here, data = df2_analysisidhere, variables = groupvar2here)|&gt;
+dplyr::filter(stat_name == 'p.value') |&gt;
+dplyr::mutate(operationid = 'Mth03_CatVar_Comp_PChiSq_1_pval')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df3_analysisidhere &lt;- 
+    cardx::ard_stats_aov(anavarhere ~ groupvar1here, data = df2_analysisidhere) |&gt;
+dplyr::filter(stat_name == 'p.value') |&gt;
+dplyr::mutate(operationid = 'Mth04_ContVar_Comp_Anova_1_pval')</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2064,24 +2109,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2118,21 +2156,21 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2448,37 +2486,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5945FE14-B7CD-4113-88D6-525465F971DD}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
         <v>313</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -2487,107 +2525,110 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF4F43AB-08A9-4D5D-BC36-392099289A62}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>474</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB264D80-6970-406C-8A9F-6A5C48FD0FE0}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>473</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44891FB9-A2CE-4D40-A988-A4A68CEC1B08}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="59.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>444</v>
       </c>
@@ -2607,7 +2648,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>449</v>
       </c>
@@ -2629,79 +2670,80 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317E84A7-ED57-45F7-86AC-94BF9578A26E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" customWidth="1"/>
-    <col min="5" max="5" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="4.5546875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="5" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="31.5546875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="33.5546875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="33.109375" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="31.88671875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>94</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="s">
@@ -2717,34 +2759,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>250</v>
       </c>
       <c r="B3" t="s">
         <v>190</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>250</v>
       </c>
       <c r="B4" t="s">
         <v>190</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="s">
@@ -2760,17 +2802,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>250</v>
       </c>
       <c r="B5" t="s">
         <v>190</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="s">
@@ -2786,34 +2828,34 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>251</v>
       </c>
       <c r="B6" t="s">
         <v>189</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>251</v>
       </c>
       <c r="B7" t="s">
         <v>189</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
@@ -2829,17 +2871,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>251</v>
       </c>
       <c r="B8" t="s">
         <v>189</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="s">
@@ -2855,34 +2897,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>252</v>
       </c>
       <c r="B9" t="s">
         <v>188</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>252</v>
       </c>
       <c r="B10" t="s">
         <v>188</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="s">
@@ -2898,17 +2940,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>252</v>
       </c>
       <c r="B11" t="s">
         <v>188</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="s">
@@ -2924,17 +2966,17 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>252</v>
       </c>
       <c r="B12" t="s">
         <v>188</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>2</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="s">
@@ -2950,34 +2992,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>253</v>
       </c>
       <c r="B13" t="s">
         <v>187</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>253</v>
       </c>
       <c r="B14" t="s">
         <v>187</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="s">
@@ -2993,17 +3035,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>253</v>
       </c>
       <c r="B15" t="s">
         <v>187</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="s">
@@ -3019,34 +3061,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>254</v>
       </c>
       <c r="B16" t="s">
         <v>191</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>254</v>
       </c>
       <c r="B17" t="s">
         <v>191</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="s">
@@ -3062,17 +3104,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>254</v>
       </c>
       <c r="B18" t="s">
         <v>191</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>2</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="s">
@@ -3088,34 +3130,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>254</v>
       </c>
       <c r="B19" t="s">
         <v>191</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>254</v>
       </c>
       <c r="B20" t="s">
         <v>191</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="s">
@@ -3131,17 +3173,17 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>254</v>
       </c>
       <c r="B21" t="s">
         <v>191</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="s">
@@ -3157,34 +3199,34 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>255</v>
       </c>
       <c r="B22" t="s">
         <v>192</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>255</v>
       </c>
       <c r="B23" t="s">
         <v>192</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>2</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="s">
@@ -3200,17 +3242,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>255</v>
       </c>
       <c r="B24" t="s">
         <v>192</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="s">
@@ -3226,34 +3268,34 @@
         <v>249</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>256</v>
       </c>
       <c r="B25" t="s">
         <v>193</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>256</v>
       </c>
       <c r="B26" t="s">
         <v>193</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>2</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="s">
@@ -3269,17 +3311,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>256</v>
       </c>
       <c r="B27" t="s">
         <v>193</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="s">
@@ -3295,17 +3337,17 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>257</v>
       </c>
       <c r="B28" t="s">
         <v>246</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="s">
@@ -3321,34 +3363,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>258</v>
       </c>
       <c r="B29" t="s">
         <v>247</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>258</v>
       </c>
       <c r="B30" t="s">
         <v>247</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="s">
@@ -3364,17 +3406,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>258</v>
       </c>
       <c r="B31" t="s">
         <v>247</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>2</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="s">
@@ -3393,68 +3435,69 @@
   </sheetData>
   <autoFilter ref="A1:L31" xr:uid="{317E84A7-ED57-45F7-86AC-94BF9578A26E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2057B85-CDD2-49FA-961B-BE66955E248E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="5" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3464,10 +3507,10 @@
       <c r="D2" t="s">
         <v>576</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="s">
@@ -3483,7 +3526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3493,10 +3536,10 @@
       <c r="D3" t="s">
         <v>577</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="s">
@@ -3514,96 +3557,97 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD49E34F-52D6-4F1E-B1C2-4599C0323EA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24.5546875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="36.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="11.21875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="37.77734375" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="22.88671875" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="23.44140625" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="26.5546875" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="43" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>325</v>
       </c>
@@ -3625,10 +3669,10 @@
       <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="s">
@@ -3644,7 +3688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -3666,10 +3710,10 @@
       <c r="I3" t="s">
         <v>35</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="P3" t="s">
@@ -3685,7 +3729,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>325</v>
       </c>
@@ -3707,10 +3751,10 @@
       <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="s">
@@ -3726,7 +3770,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>322</v>
       </c>
@@ -3748,10 +3792,10 @@
       <c r="I5" t="s">
         <v>28</v>
       </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="s">
@@ -3767,7 +3811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>322</v>
       </c>
@@ -3789,10 +3833,10 @@
       <c r="I6" t="s">
         <v>33</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="s">
@@ -3808,7 +3852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -3830,10 +3874,10 @@
       <c r="I7" t="s">
         <v>39</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="s">
@@ -3849,7 +3893,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -3871,10 +3915,10 @@
       <c r="I8" t="s">
         <v>80</v>
       </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="s">
@@ -3890,7 +3934,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -3912,10 +3956,10 @@
       <c r="I9" t="s">
         <v>82</v>
       </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="s">
@@ -3931,7 +3975,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3953,10 +3997,10 @@
       <c r="I10" t="s">
         <v>46</v>
       </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="s">
@@ -3972,7 +4016,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -3994,10 +4038,10 @@
       <c r="I11" t="s">
         <v>47</v>
       </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="s">
@@ -4013,7 +4057,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -4035,10 +4079,10 @@
       <c r="I12" t="s">
         <v>83</v>
       </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="s">
@@ -4054,7 +4098,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -4076,10 +4120,10 @@
       <c r="I13" t="s">
         <v>48</v>
       </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
       <c r="P13" t="s">
@@ -4095,7 +4139,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -4117,10 +4161,10 @@
       <c r="I14" t="s">
         <v>49</v>
       </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>6</v>
       </c>
       <c r="P14" t="s">
@@ -4136,7 +4180,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -4158,10 +4202,10 @@
       <c r="I15" t="s">
         <v>50</v>
       </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>7</v>
       </c>
       <c r="P15" t="s">
@@ -4177,7 +4221,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -4199,10 +4243,10 @@
       <c r="I16" t="s">
         <v>51</v>
       </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="s">
@@ -4218,7 +4262,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -4240,10 +4284,10 @@
       <c r="I17" t="s">
         <v>52</v>
       </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>9</v>
       </c>
       <c r="P17" t="s">
@@ -4259,7 +4303,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -4281,10 +4325,10 @@
       <c r="I18" t="s">
         <v>84</v>
       </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="s">
@@ -4300,7 +4344,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -4322,10 +4366,10 @@
       <c r="I19" t="s">
         <v>85</v>
       </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="P19" t="s">
@@ -4341,7 +4385,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>210</v>
       </c>
@@ -4363,10 +4407,10 @@
       <c r="I20" t="s">
         <v>216</v>
       </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="s">
@@ -4382,7 +4426,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>210</v>
       </c>
@@ -4404,10 +4448,10 @@
       <c r="I21" t="s">
         <v>213</v>
       </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="s">
@@ -4423,7 +4467,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>210</v>
       </c>
@@ -4445,10 +4489,10 @@
       <c r="I22" t="s">
         <v>219</v>
       </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="P22" t="s">
@@ -4464,7 +4508,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>210</v>
       </c>
@@ -4486,10 +4530,10 @@
       <c r="I23" t="s">
         <v>218</v>
       </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="s">
@@ -4505,7 +4549,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>226</v>
       </c>
@@ -4527,10 +4571,10 @@
       <c r="I24" t="s">
         <v>228</v>
       </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="s">
@@ -4546,7 +4590,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>226</v>
       </c>
@@ -4568,10 +4612,10 @@
       <c r="I25" t="s">
         <v>229</v>
       </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="P25" t="s">
@@ -4587,7 +4631,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>226</v>
       </c>
@@ -4609,10 +4653,10 @@
       <c r="I26" t="s">
         <v>230</v>
       </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="s">
@@ -4628,7 +4672,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>226</v>
       </c>
@@ -4650,10 +4694,10 @@
       <c r="I27" t="s">
         <v>231</v>
       </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="P27" t="s">
@@ -4669,7 +4713,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>226</v>
       </c>
@@ -4691,10 +4735,10 @@
       <c r="I28" t="s">
         <v>232</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>5</v>
       </c>
       <c r="P28" t="s">
@@ -4710,7 +4754,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>226</v>
       </c>
@@ -4732,10 +4776,10 @@
       <c r="I29" t="s">
         <v>233</v>
       </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
         <v>6</v>
       </c>
       <c r="P29" t="s">
@@ -4751,7 +4795,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>226</v>
       </c>
@@ -4773,10 +4817,10 @@
       <c r="I30" t="s">
         <v>234</v>
       </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
         <v>7</v>
       </c>
       <c r="P30" t="s">
@@ -4792,7 +4836,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>226</v>
       </c>
@@ -4814,10 +4858,10 @@
       <c r="I31" t="s">
         <v>235</v>
       </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
         <v>8</v>
       </c>
       <c r="P31" t="s">
@@ -4833,7 +4877,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>226</v>
       </c>
@@ -4855,10 +4899,10 @@
       <c r="I32" t="s">
         <v>236</v>
       </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>9</v>
       </c>
       <c r="P32" t="s">
@@ -4874,7 +4918,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>226</v>
       </c>
@@ -4896,10 +4940,10 @@
       <c r="I33" t="s">
         <v>237</v>
       </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
         <v>10</v>
       </c>
       <c r="P33" t="s">
@@ -4915,7 +4959,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>226</v>
       </c>
@@ -4937,10 +4981,10 @@
       <c r="I34" t="s">
         <v>238</v>
       </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
         <v>11</v>
       </c>
       <c r="P34" t="s">
@@ -4957,119 +5001,118 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB53023-B5E5-496E-A786-48C47411B817}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:W24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="88.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="40.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="56.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="38.88671875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="88.44140625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="29.88671875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.77734375" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="23.44140625" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="10.109375" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="27.33203125" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="52.77734375" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="40.77734375" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="52.77734375" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="40.77734375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>385</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -5103,17 +5146,17 @@
         <v>494</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>386</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F3" t="s">
@@ -5144,17 +5187,17 @@
         <v>280</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>387</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>271</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F4" t="s">
@@ -5185,17 +5228,17 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>388</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F5" t="s">
@@ -5244,17 +5287,17 @@
         <v>385</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>389</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>273</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
@@ -5291,17 +5334,17 @@
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>390</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>167</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F7" t="s">
@@ -5350,17 +5393,17 @@
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>391</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F8" t="s">
@@ -5397,17 +5440,17 @@
         <v>274</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>392</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F9" t="s">
@@ -5456,17 +5499,17 @@
         <v>385</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>393</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>276</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F10" t="s">
@@ -5503,17 +5546,17 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>394</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>308</v>
       </c>
       <c r="F11" t="s">
@@ -5562,17 +5605,17 @@
         <v>385</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>395</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>277</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>308</v>
       </c>
       <c r="F12" t="s">
@@ -5609,17 +5652,17 @@
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>396</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>309</v>
       </c>
       <c r="F13" t="s">
@@ -5650,17 +5693,17 @@
         <v>280</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>397</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>309</v>
       </c>
       <c r="F14" t="s">
@@ -5691,11 +5734,11 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>398</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -5747,11 +5790,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>401</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -5803,11 +5846,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>402</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="s">
@@ -5859,11 +5902,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>403</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="s">
@@ -5915,11 +5958,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>404</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -5971,11 +6014,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>405</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="s">
@@ -6027,11 +6070,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>406</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="s">
@@ -6083,11 +6126,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>407</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="s">
@@ -6139,11 +6182,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>414</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="s">
@@ -6192,11 +6235,11 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>415</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="s">
@@ -6247,137 +6290,135 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W24" xr:uid="{4AB53023-B5E5-496E-A786-48C47411B817}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S13">
-    <sortCondition ref="A1:A13"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7330FD-BC60-4063-AD51-1ADCE1E2B7CF}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="D7" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{1F7330FD-BC60-4063-AD51-1ADCE1E2B7CF}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7" xr:uid="{93C20FD9-A520-4F19-96A5-76364810E4EA}">
       <formula1>"Code,DocumentRef"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FCEEFCB-4AF8-4DF4-9DD6-EB21C9658A74}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>473</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E9726D-99E8-44E0-8F39-A719318C5D2B}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="59.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>385</v>
       </c>
@@ -6393,11 +6434,11 @@
       <c r="E2" t="s">
         <v>438</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>386</v>
       </c>
@@ -6413,11 +6454,11 @@
       <c r="E3" t="s">
         <v>436</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>387</v>
       </c>
@@ -6433,11 +6474,11 @@
       <c r="E4" t="s">
         <v>436</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>388</v>
       </c>
@@ -6453,11 +6494,11 @@
       <c r="E5" t="s">
         <v>436</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>389</v>
       </c>
@@ -6473,11 +6514,11 @@
       <c r="E6" t="s">
         <v>436</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>390</v>
       </c>
@@ -6493,11 +6534,11 @@
       <c r="E7" t="s">
         <v>436</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>391</v>
       </c>
@@ -6513,11 +6554,11 @@
       <c r="E8" t="s">
         <v>436</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>392</v>
       </c>
@@ -6533,11 +6574,11 @@
       <c r="E9" t="s">
         <v>436</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>393</v>
       </c>
@@ -6553,11 +6594,11 @@
       <c r="E10" t="s">
         <v>436</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>394</v>
       </c>
@@ -6573,11 +6614,11 @@
       <c r="E11" t="s">
         <v>436</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -6593,11 +6634,11 @@
       <c r="E12" t="s">
         <v>436</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>396</v>
       </c>
@@ -6613,11 +6654,11 @@
       <c r="E13" t="s">
         <v>436</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>397</v>
       </c>
@@ -6633,11 +6674,11 @@
       <c r="E14" t="s">
         <v>436</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>398</v>
       </c>
@@ -6657,7 +6698,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>399</v>
       </c>
@@ -6677,7 +6718,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>400</v>
       </c>
@@ -6697,7 +6738,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>408</v>
       </c>
@@ -6717,7 +6758,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>409</v>
       </c>
@@ -6737,7 +6778,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>410</v>
       </c>
@@ -6757,7 +6798,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>411</v>
       </c>
@@ -6777,7 +6818,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>412</v>
       </c>
@@ -6797,7 +6838,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>413</v>
       </c>
@@ -6817,7 +6858,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>414</v>
       </c>
@@ -6837,7 +6878,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>415</v>
       </c>
@@ -6853,11 +6894,11 @@
       <c r="E25" t="s">
         <v>521</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>415</v>
       </c>
@@ -6873,11 +6914,11 @@
       <c r="E26" t="s">
         <v>522</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>415</v>
       </c>
@@ -6905,39 +6946,41 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63425975-7444-4301-ABB6-796B2115B6F2}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.21875" customWidth="1"/>
-    <col min="2" max="3" width="34.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="43.88671875" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="34.109375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="43.88671875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>424</v>
       </c>
@@ -6948,7 +6991,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>425</v>
       </c>
@@ -6959,7 +7002,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>480</v>
       </c>
@@ -6970,7 +7013,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>518</v>
       </c>
@@ -6983,100 +7026,101 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC97203C-D8B1-4020-B955-08EA542F4944}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:T14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="63" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="156.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="63" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="50.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="201.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="88.21875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="59.88671875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25.77734375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.21875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="41.77734375" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="63" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="48.77734375" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="156.5546875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="41.77734375" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="63" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="50.5546875" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="48.77734375" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="201.33203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>494</v>
       </c>
@@ -7098,14 +7142,14 @@
       <c r="H2" t="s">
         <v>63</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>279</v>
       </c>
@@ -7127,14 +7171,14 @@
       <c r="H3" t="s">
         <v>63</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>279</v>
       </c>
@@ -7156,7 +7200,7 @@
       <c r="H4" t="s">
         <v>77</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="s">
@@ -7187,7 +7231,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>280</v>
       </c>
@@ -7209,14 +7253,14 @@
       <c r="H5" t="s">
         <v>63</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -7238,14 +7282,14 @@
       <c r="H6" t="s">
         <v>64</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -7267,14 +7311,14 @@
       <c r="H7" t="s">
         <v>65</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>280</v>
       </c>
@@ -7296,14 +7340,14 @@
       <c r="H8" t="s">
         <v>66</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>280</v>
       </c>
@@ -7325,14 +7369,14 @@
       <c r="H9" t="s">
         <v>67</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>280</v>
       </c>
@@ -7354,14 +7398,14 @@
       <c r="H10" t="s">
         <v>68</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>280</v>
       </c>
@@ -7383,14 +7427,14 @@
       <c r="H11" t="s">
         <v>69</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>280</v>
       </c>
@@ -7412,14 +7456,14 @@
       <c r="H12" t="s">
         <v>70</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>274</v>
       </c>
@@ -7441,14 +7485,14 @@
       <c r="H13" t="s">
         <v>297</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>272</v>
       </c>
@@ -7470,7 +7514,7 @@
       <c r="H14" t="s">
         <v>297</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="s">
@@ -7478,45 +7522,42 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:M32">
-    <sortCondition ref="A5:A32"/>
-    <sortCondition ref="I5:I32"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5A7EA2-5BB8-48A0-AE19-CC45569B1AA0}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="93.33203125" customWidth="1"/>
-    <col min="5" max="5" width="91.109375" customWidth="1"/>
-    <col min="6" max="6" width="48.88671875" customWidth="1"/>
-    <col min="7" max="7" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="93.33203125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="91.109375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="48.88671875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="34.88671875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="144" customHeight="1">
       <c r="A2" t="s">
         <v>494</v>
       </c>
@@ -7527,12 +7568,12 @@
         <v>468</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="3" ht="388.8" customHeight="1">
       <c r="A3" t="s">
         <v>279</v>
       </c>
@@ -7543,12 +7584,12 @@
         <v>468</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="4" ht="201.6" customHeight="1">
       <c r="A4" t="s">
         <v>280</v>
       </c>
@@ -7559,12 +7600,12 @@
         <v>468</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" ht="57.6" customHeight="1">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -7575,11 +7616,11 @@
         <v>468</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" ht="57.6" customHeight="1">
       <c r="A6" t="s">
         <v>272</v>
       </c>
@@ -7590,53 +7631,53 @@
         <v>468</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="E7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F5578B-A7DE-401B-B867-DFECFDE9AF0A}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
-    <col min="5" max="5" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="73.88671875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>494</v>
       </c>
@@ -7650,7 +7691,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>494</v>
       </c>
@@ -7664,7 +7705,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>494</v>
       </c>
@@ -7678,7 +7719,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -7692,7 +7733,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>279</v>
       </c>
@@ -7706,7 +7747,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>279</v>
       </c>
@@ -7720,7 +7761,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>279</v>
       </c>
@@ -7734,7 +7775,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>279</v>
       </c>
@@ -7748,7 +7789,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>279</v>
       </c>
@@ -7762,7 +7803,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>279</v>
       </c>
@@ -7776,7 +7817,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>280</v>
       </c>
@@ -7790,7 +7831,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>280</v>
       </c>
@@ -7804,7 +7845,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>274</v>
       </c>
@@ -7818,7 +7859,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>274</v>
       </c>
@@ -7832,7 +7873,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>272</v>
       </c>
@@ -7846,7 +7887,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>272</v>
       </c>
@@ -7861,45 +7902,45 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26572EB2-03E0-4576-A1FD-245E2B761D42}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="59.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>280</v>
       </c>
@@ -7915,11 +7956,11 @@
       <c r="E2" t="s">
         <v>441</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>279</v>
       </c>
@@ -7935,7 +7976,7 @@
       <c r="E3" t="s">
         <v>441</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7949,39 +7990,40 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C6F21E-B0BD-4A7C-9873-05E64DE79965}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.44140625" customWidth="1"/>
-    <col min="5" max="5" width="52.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="52.77734375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>384</v>
       </c>
@@ -8008,40 +8050,40 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A19ABE-6E7C-4DBB-B149-CB6DE6FC596E}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>331</v>
       </c>
@@ -8055,7 +8097,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>331</v>
       </c>
@@ -8069,7 +8111,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>331</v>
       </c>
@@ -8083,7 +8125,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>350</v>
       </c>
@@ -8097,7 +8139,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>350</v>
       </c>
@@ -8111,7 +8153,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>350</v>
       </c>
@@ -8125,7 +8167,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>363</v>
       </c>
@@ -8142,7 +8184,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>364</v>
       </c>
@@ -8159,7 +8201,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>364</v>
       </c>
@@ -8176,7 +8218,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>364</v>
       </c>
@@ -8193,7 +8235,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>365</v>
       </c>
@@ -8210,7 +8252,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>365</v>
       </c>
@@ -8227,7 +8269,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>366</v>
       </c>
@@ -8244,7 +8286,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>366</v>
       </c>
@@ -8261,7 +8303,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>367</v>
       </c>
@@ -8278,7 +8320,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>367</v>
       </c>
@@ -8297,135 +8339,135 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04E4817-59BC-4505-A834-22FE96EF578C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:M40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="58.44140625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="37.21875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>534</v>
       </c>
       <c r="C2" t="s">
         <v>537</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>115</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>534</v>
       </c>
       <c r="C3" t="s">
         <v>537</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>534</v>
       </c>
       <c r="C4" t="s">
         <v>537</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>534</v>
       </c>
       <c r="C5" t="s">
         <v>537</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5">
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="s">
@@ -8438,22 +8480,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>534</v>
       </c>
       <c r="C6" t="s">
         <v>537</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="s">
@@ -8466,22 +8508,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>534</v>
       </c>
       <c r="C7" t="s">
         <v>537</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="s">
@@ -8491,22 +8533,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>534</v>
       </c>
       <c r="C8" t="s">
         <v>537</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="s">
@@ -8519,22 +8561,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>534</v>
       </c>
       <c r="C9" t="s">
         <v>537</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="s">
@@ -8547,22 +8589,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>534</v>
       </c>
       <c r="C10" t="s">
         <v>537</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="s">
@@ -8572,22 +8614,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>534</v>
       </c>
       <c r="C11" t="s">
         <v>537</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="s">
@@ -8600,22 +8642,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>534</v>
       </c>
       <c r="C12" t="s">
         <v>537</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12">
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="s">
@@ -8628,22 +8670,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>534</v>
       </c>
       <c r="C13" t="s">
         <v>537</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="s">
@@ -8653,22 +8695,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>534</v>
       </c>
       <c r="C14" t="s">
         <v>537</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="s">
@@ -8681,22 +8723,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>534</v>
       </c>
       <c r="C15" t="s">
         <v>537</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15">
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="s">
@@ -8709,22 +8751,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>534</v>
       </c>
       <c r="C16" t="s">
         <v>537</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="s">
@@ -8734,22 +8776,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>534</v>
       </c>
       <c r="C17" t="s">
         <v>537</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="s">
@@ -8762,22 +8804,22 @@
         <v>444</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>534</v>
       </c>
       <c r="C18" t="s">
         <v>537</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="s">
@@ -8790,22 +8832,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>534</v>
       </c>
       <c r="C19" t="s">
         <v>537</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="s">
@@ -8815,22 +8857,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>534</v>
       </c>
       <c r="C20" t="s">
         <v>537</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20">
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="s">
@@ -8843,22 +8885,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>534</v>
       </c>
       <c r="C21" t="s">
         <v>537</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21">
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="s">
@@ -8871,22 +8913,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>534</v>
       </c>
       <c r="C22" t="s">
         <v>537</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22">
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="s">
@@ -8899,22 +8941,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>534</v>
       </c>
       <c r="C23" t="s">
         <v>537</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="s">
@@ -8927,22 +8969,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>534</v>
       </c>
       <c r="C24" t="s">
         <v>537</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="L24" t="s">
@@ -8952,22 +8994,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>534</v>
       </c>
       <c r="C25" t="s">
         <v>537</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="s">
@@ -8980,22 +9022,22 @@
         <v>449</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>534</v>
       </c>
       <c r="C26" t="s">
         <v>537</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="s">
@@ -9008,308 +9050,308 @@
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>534</v>
       </c>
       <c r="C27" t="s">
         <v>537</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" t="n">
         <v>3</v>
       </c>
       <c r="I27" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>534</v>
       </c>
       <c r="C28" t="s">
         <v>537</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>534</v>
       </c>
       <c r="C29" t="s">
         <v>537</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29">
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" t="n">
         <v>5</v>
       </c>
       <c r="I29" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>534</v>
       </c>
       <c r="C30" t="s">
         <v>537</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" t="n">
         <v>6</v>
       </c>
       <c r="I30" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>534</v>
       </c>
       <c r="C31" t="s">
         <v>537</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" t="n">
         <v>7</v>
       </c>
       <c r="I31" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>534</v>
       </c>
       <c r="C32" t="s">
         <v>537</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" t="n">
         <v>8</v>
       </c>
       <c r="I32" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>534</v>
       </c>
       <c r="C33" t="s">
         <v>537</v>
       </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>534</v>
       </c>
       <c r="C34" t="s">
         <v>537</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" t="s">
         <v>534</v>
       </c>
       <c r="C35" t="s">
         <v>537</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" t="n">
         <v>2</v>
       </c>
       <c r="I35" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" t="s">
         <v>534</v>
       </c>
       <c r="C36" t="s">
         <v>537</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" t="n">
         <v>3</v>
       </c>
       <c r="I36" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" t="s">
         <v>534</v>
       </c>
       <c r="C37" t="s">
         <v>537</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" t="n">
         <v>5</v>
       </c>
       <c r="J37" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" t="s">
         <v>534</v>
       </c>
       <c r="C38" t="s">
         <v>537</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" t="s">
         <v>534</v>
       </c>
       <c r="C39" t="s">
         <v>537</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39">
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" t="s">
         <v>534</v>
       </c>
       <c r="C40" t="s">
         <v>537</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40">
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" t="n">
         <v>3</v>
       </c>
       <c r="I40" t="s">
@@ -9317,138 +9359,137 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78005A0C-8AA5-4998-8A42-428CFBB35FD9}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="80.109375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>535</v>
       </c>
       <c r="C2" t="s">
         <v>536</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>115</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>535</v>
       </c>
       <c r="C3" t="s">
         <v>536</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>535</v>
       </c>
       <c r="C4" t="s">
         <v>536</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>535</v>
       </c>
       <c r="C5" t="s">
         <v>536</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="s">
@@ -9457,32 +9498,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC151BBF-2F10-45B4-986C-600EDF05B350}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="64.88671875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>568</v>
       </c>
@@ -9493,7 +9534,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>568</v>
       </c>
@@ -9504,7 +9545,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -9515,7 +9556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>566</v>
       </c>
@@ -9527,129 +9568,129 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A26" xr:uid="{126A0BF0-0491-484D-A2C5-21C668CFA0AD}">
       <formula1>"Header,Title,Rowlabel Header,Legend,Abbreviation,Footnote,Footer"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B8F6BB7-6ECF-4265-9AA7-E57DC9AB4DDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="78.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="40.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="7" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="78.77734375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="40.88671875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>444</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>428</v>
       </c>
       <c r="G2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>449</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="5" t="s">
         <v>429</v>
       </c>
       <c r="G3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>456</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="5" t="s">
         <v>430</v>
       </c>
       <c r="G4" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>458</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="5" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9658,47 +9699,48 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E796BA-3F1D-473E-B665-46DA5BD6D07D}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>444</v>
       </c>
@@ -9708,14 +9750,14 @@
       <c r="D2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>541</v>
       </c>
       <c r="F2" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>444</v>
       </c>
@@ -9725,14 +9767,14 @@
       <c r="D3" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>542</v>
       </c>
       <c r="F3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>449</v>
       </c>
@@ -9742,14 +9784,14 @@
       <c r="D4" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>543</v>
       </c>
       <c r="F4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>449</v>
       </c>
@@ -9759,14 +9801,14 @@
       <c r="D5" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>544</v>
       </c>
       <c r="F5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>456</v>
       </c>
@@ -9776,14 +9818,14 @@
       <c r="D6" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>545</v>
       </c>
       <c r="F6" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>456</v>
       </c>
@@ -9793,14 +9835,14 @@
       <c r="D7" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>546</v>
       </c>
       <c r="F7" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>458</v>
       </c>
@@ -9810,14 +9852,14 @@
       <c r="D8" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>547</v>
       </c>
       <c r="F8" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>458</v>
       </c>
@@ -9827,7 +9869,7 @@
       <c r="D9" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>548</v>
       </c>
       <c r="F9" t="s">
@@ -9836,60 +9878,61 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3266631C-B97C-414A-AC8B-8A56E4E40917}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="79.6640625" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="7" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="79.6640625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="29" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="27.109375" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="54.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>445</v>
       </c>
@@ -9899,7 +9942,7 @@
       <c r="D2" t="s">
         <v>146</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -9908,14 +9951,14 @@
       <c r="G2" t="s">
         <v>568</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>445</v>
       </c>
@@ -9925,7 +9968,7 @@
       <c r="D3" t="s">
         <v>146</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -9934,14 +9977,14 @@
       <c r="G3" t="s">
         <v>568</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>445</v>
       </c>
@@ -9951,7 +9994,7 @@
       <c r="D4" t="s">
         <v>146</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="s">
@@ -9960,7 +10003,7 @@
       <c r="G4" t="s">
         <v>135</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="s">
@@ -9970,7 +10013,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>445</v>
       </c>
@@ -9980,7 +10023,7 @@
       <c r="D5" t="s">
         <v>146</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="s">
@@ -9989,7 +10032,7 @@
       <c r="G5" t="s">
         <v>135</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="s">
@@ -9999,7 +10042,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>445</v>
       </c>
@@ -10009,7 +10052,7 @@
       <c r="D6" t="s">
         <v>146</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -10018,14 +10061,14 @@
       <c r="G6" t="s">
         <v>135</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>445</v>
       </c>
@@ -10035,7 +10078,7 @@
       <c r="D7" t="s">
         <v>146</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="s">
@@ -10044,7 +10087,7 @@
       <c r="G7" t="s">
         <v>566</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
@@ -10054,7 +10097,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>445</v>
       </c>
@@ -10064,7 +10107,7 @@
       <c r="D8" t="s">
         <v>146</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="s">
@@ -10073,14 +10116,14 @@
       <c r="G8" t="s">
         <v>566</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>445</v>
       </c>
@@ -10090,7 +10133,7 @@
       <c r="D9" t="s">
         <v>146</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="s">
@@ -10099,7 +10142,7 @@
       <c r="G9" t="s">
         <v>140</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="s">
@@ -10109,7 +10152,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>450</v>
       </c>
@@ -10119,7 +10162,7 @@
       <c r="D10" t="s">
         <v>196</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="s">
@@ -10128,14 +10171,14 @@
       <c r="G10" t="s">
         <v>568</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>450</v>
       </c>
@@ -10145,7 +10188,7 @@
       <c r="D11" t="s">
         <v>196</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="s">
@@ -10154,14 +10197,14 @@
       <c r="G11" t="s">
         <v>568</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>450</v>
       </c>
@@ -10171,7 +10214,7 @@
       <c r="D12" t="s">
         <v>196</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="s">
@@ -10180,7 +10223,7 @@
       <c r="G12" t="s">
         <v>135</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="s">
@@ -10190,7 +10233,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>450</v>
       </c>
@@ -10200,7 +10243,7 @@
       <c r="D13" t="s">
         <v>196</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="s">
@@ -10209,7 +10252,7 @@
       <c r="G13" t="s">
         <v>135</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="s">
@@ -10219,7 +10262,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>450</v>
       </c>
@@ -10229,7 +10272,7 @@
       <c r="D14" t="s">
         <v>196</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="s">
@@ -10238,14 +10281,14 @@
       <c r="G14" t="s">
         <v>135</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>450</v>
       </c>
@@ -10255,7 +10298,7 @@
       <c r="D15" t="s">
         <v>196</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="s">
@@ -10264,7 +10307,7 @@
       <c r="G15" t="s">
         <v>143</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="s">
@@ -10274,7 +10317,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>450</v>
       </c>
@@ -10284,7 +10327,7 @@
       <c r="D16" t="s">
         <v>196</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="s">
@@ -10293,7 +10336,7 @@
       <c r="G16" t="s">
         <v>139</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="s">
@@ -10303,7 +10346,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>450</v>
       </c>
@@ -10313,7 +10356,7 @@
       <c r="D17" t="s">
         <v>196</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="s">
@@ -10322,7 +10365,7 @@
       <c r="G17" t="s">
         <v>566</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="s">
@@ -10332,7 +10375,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>450</v>
       </c>
@@ -10342,7 +10385,7 @@
       <c r="D18" t="s">
         <v>196</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="s">
@@ -10351,14 +10394,14 @@
       <c r="G18" t="s">
         <v>566</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>450</v>
       </c>
@@ -10368,7 +10411,7 @@
       <c r="D19" t="s">
         <v>196</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="s">
@@ -10377,7 +10420,7 @@
       <c r="G19" t="s">
         <v>140</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="s">
@@ -10387,7 +10430,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>457</v>
       </c>
@@ -10397,23 +10440,23 @@
       <c r="D20" t="s">
         <v>201</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G20" t="s">
         <v>568</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>457</v>
       </c>
@@ -10423,23 +10466,23 @@
       <c r="D21" t="s">
         <v>201</v>
       </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G21" t="s">
         <v>568</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>457</v>
       </c>
@@ -10449,16 +10492,16 @@
       <c r="D22" t="s">
         <v>201</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G22" t="s">
         <v>135</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="s">
@@ -10468,7 +10511,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>457</v>
       </c>
@@ -10478,16 +10521,16 @@
       <c r="D23" t="s">
         <v>201</v>
       </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G23" t="s">
         <v>135</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>2</v>
       </c>
       <c r="I23" t="s">
@@ -10497,7 +10540,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>457</v>
       </c>
@@ -10507,23 +10550,23 @@
       <c r="D24" t="s">
         <v>201</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G24" t="s">
         <v>135</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>457</v>
       </c>
@@ -10533,16 +10576,16 @@
       <c r="D25" t="s">
         <v>201</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G25" t="s">
         <v>144</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="s">
@@ -10552,7 +10595,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" t="s">
         <v>457</v>
       </c>
@@ -10562,16 +10605,16 @@
       <c r="D26" t="s">
         <v>201</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G26" t="s">
         <v>566</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="s">
@@ -10581,7 +10624,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" t="s">
         <v>457</v>
       </c>
@@ -10591,23 +10634,23 @@
       <c r="D27" t="s">
         <v>201</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G27" t="s">
         <v>566</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" t="s">
         <v>457</v>
       </c>
@@ -10617,16 +10660,16 @@
       <c r="D28" t="s">
         <v>201</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G28" t="s">
         <v>140</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="s">
@@ -10636,7 +10679,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" t="s">
         <v>457</v>
       </c>
@@ -10646,16 +10689,16 @@
       <c r="D29" t="s">
         <v>201</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="s">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G29" t="s">
         <v>140</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>2</v>
       </c>
       <c r="I29" t="s">
@@ -10665,7 +10708,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" t="s">
         <v>459</v>
       </c>
@@ -10675,23 +10718,23 @@
       <c r="D30" t="s">
         <v>206</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G30" t="s">
         <v>568</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" t="s">
         <v>459</v>
       </c>
@@ -10701,23 +10744,23 @@
       <c r="D31" t="s">
         <v>206</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G31" t="s">
         <v>568</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" t="s">
         <v>459</v>
       </c>
@@ -10727,16 +10770,16 @@
       <c r="D32" t="s">
         <v>206</v>
       </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G32" t="s">
         <v>135</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="s">
@@ -10746,7 +10789,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" t="s">
         <v>459</v>
       </c>
@@ -10756,23 +10799,23 @@
       <c r="D33" t="s">
         <v>206</v>
       </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G33" t="s">
         <v>135</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" t="s">
         <v>459</v>
       </c>
@@ -10782,23 +10825,23 @@
       <c r="D34" t="s">
         <v>206</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G34" t="s">
         <v>135</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>3</v>
       </c>
       <c r="I34" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" t="s">
         <v>459</v>
       </c>
@@ -10808,23 +10851,23 @@
       <c r="D35" t="s">
         <v>206</v>
       </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G35" t="s">
         <v>144</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" t="s">
         <v>459</v>
       </c>
@@ -10834,23 +10877,23 @@
       <c r="D36" t="s">
         <v>206</v>
       </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="s">
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G36" t="s">
         <v>566</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" t="s">
         <v>459</v>
       </c>
@@ -10860,23 +10903,23 @@
       <c r="D37" t="s">
         <v>206</v>
       </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G37" t="s">
         <v>566</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>2</v>
       </c>
       <c r="I37" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" t="s">
         <v>459</v>
       </c>
@@ -10886,23 +10929,23 @@
       <c r="D38" t="s">
         <v>206</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="s">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G38" t="s">
         <v>140</v>
       </c>
-      <c r="H38">
+      <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" t="s">
         <v>459</v>
       </c>
@@ -10912,16 +10955,16 @@
       <c r="D39" t="s">
         <v>206</v>
       </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="s">
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G39" t="s">
         <v>140</v>
       </c>
-      <c r="H39">
+      <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="s">
@@ -10930,7 +10973,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J39" xr:uid="{3266631C-B97C-414A-AC8B-8A56E4E40917}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>